--- a/83/food/tm2026-sm.xlsx
+++ b/83/food/tm2026-sm.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7935" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
@@ -506,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -644,6 +644,12 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1065,12 +1071,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L196"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="4.7109375" customWidth="1" style="2" min="1" max="1"/>
     <col width="5.28515625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="9.140625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="11.5703125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="50" min="3" max="3"/>
+    <col width="11.5703125" customWidth="1" style="50" min="4" max="4"/>
     <col width="52.5703125" customWidth="1" style="2" min="5" max="5"/>
     <col width="9.28515625" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="7"/>
@@ -1082,18 +1088,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Школа</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>МБОУ «СОШ №1 ст.Ассиновская»</t>
         </is>
       </c>
-      <c r="D1" s="58" t="n"/>
-      <c r="E1" s="59" t="n"/>
+      <c r="D1" s="60" t="n"/>
+      <c r="E1" s="61" t="n"/>
       <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Утвердил:</t>
@@ -1104,14 +1110,14 @@
           <t>должность</t>
         </is>
       </c>
-      <c r="H1" s="57" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Директор</t>
         </is>
       </c>
-      <c r="I1" s="58" t="n"/>
-      <c r="J1" s="58" t="n"/>
-      <c r="K1" s="59" t="n"/>
+      <c r="I1" s="60" t="n"/>
+      <c r="J1" s="60" t="n"/>
+      <c r="K1" s="61" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
@@ -1125,14 +1131,14 @@
           <t>фамилия</t>
         </is>
       </c>
-      <c r="H2" s="57" t="inlineStr">
+      <c r="H2" s="59" t="inlineStr">
         <is>
           <t>Бехоева Макка Магомедовна</t>
         </is>
       </c>
-      <c r="I2" s="58" t="n"/>
-      <c r="J2" s="58" t="n"/>
-      <c r="K2" s="59" t="n"/>
+      <c r="I2" s="60" t="n"/>
+      <c r="J2" s="60" t="n"/>
+      <c r="K2" s="61" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1161,7 +1167,7 @@
       <c r="J3" s="49" t="n">
         <v>2026</v>
       </c>
-      <c r="K3" s="1" t="n"/>
+      <c r="K3" s="50" t="n"/>
     </row>
     <row r="4" ht="13.5" customHeight="1" thickBot="1">
       <c r="C4" s="2" t="n"/>
@@ -1244,7 +1250,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="20" t="n">
         <v>1</v>
       </c>
@@ -1292,7 +1298,7 @@
       <c r="A7" s="23" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="11" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
@@ -1533,14 +1539,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E15" s="42" t="n"/>
-      <c r="F15" s="43" t="n"/>
-      <c r="G15" s="43" t="n"/>
-      <c r="H15" s="43" t="n"/>
-      <c r="I15" s="43" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="44" t="n"/>
-      <c r="L15" s="43" t="n"/>
+      <c r="E15" s="42" t="inlineStr">
+        <is>
+          <t>Суп картофельный с бобовыми №113</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H15" s="43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I15" s="43" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="J15" s="43" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="K15" s="44" t="n">
+        <v>113</v>
+      </c>
+      <c r="L15" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="23" t="n"/>
@@ -1551,14 +1575,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E16" s="42" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="43" t="n"/>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
-      <c r="J16" s="43" t="n"/>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H16" s="43" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J16" s="43" t="n">
+        <v>262.7</v>
+      </c>
       <c r="K16" s="44" t="n"/>
-      <c r="L16" s="43" t="n"/>
+      <c r="L16" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="23" t="n"/>
@@ -1569,14 +1609,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E17" s="42" t="n"/>
-      <c r="F17" s="43" t="n"/>
-      <c r="G17" s="43" t="n"/>
-      <c r="H17" s="43" t="n"/>
-      <c r="I17" s="43" t="n"/>
-      <c r="J17" s="43" t="n"/>
-      <c r="K17" s="44" t="n"/>
-      <c r="L17" s="43" t="n"/>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t>Греча отварная №4.3</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="H17" s="43" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I17" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J17" s="43" t="n">
+        <v>243.73</v>
+      </c>
+      <c r="K17" s="44" t="n">
+        <v>313</v>
+      </c>
+      <c r="L17" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="23" t="n"/>
@@ -1587,14 +1645,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E18" s="42" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="n"/>
-      <c r="I18" s="43" t="n"/>
-      <c r="J18" s="43" t="n"/>
-      <c r="K18" s="44" t="n"/>
-      <c r="L18" s="43" t="n"/>
+      <c r="E18" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H18" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I18" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J18" s="43" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K18" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L18" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="23" t="n"/>
@@ -1605,14 +1681,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E19" s="42" t="n"/>
-      <c r="F19" s="43" t="n"/>
-      <c r="G19" s="43" t="n"/>
-      <c r="H19" s="43" t="n"/>
-      <c r="I19" s="43" t="n"/>
-      <c r="J19" s="43" t="n"/>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H19" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I19" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J19" s="43" t="n">
+        <v>187.04</v>
+      </c>
       <c r="K19" s="44" t="n"/>
-      <c r="L19" s="43" t="n"/>
+      <c r="L19" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="23" t="n"/>
@@ -1705,12 +1797,12 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D24" s="61" t="n"/>
+      <c r="D24" s="63" t="n"/>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="32">
         <f>F13+F23</f>
@@ -1757,7 +1849,7 @@
       </c>
       <c r="E25" s="39" t="inlineStr">
         <is>
-          <t>Каша рисовая с изюмом</t>
+          <t>Каша рисовая с изюмом №177</t>
         </is>
       </c>
       <c r="F25" s="40" t="n">
@@ -1778,7 +1870,7 @@
       <c r="K25" s="41" t="n">
         <v>177</v>
       </c>
-      <c r="L25" s="50" t="n">
+      <c r="L25" s="52" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1794,7 +1886,7 @@
       <c r="I26" s="43" t="n"/>
       <c r="J26" s="43" t="n"/>
       <c r="K26" s="44" t="n"/>
-      <c r="L26" s="51" t="n"/>
+      <c r="L26" s="43" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="14" t="n"/>
@@ -1807,7 +1899,7 @@
       </c>
       <c r="E27" s="42" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками</t>
+          <t>Чай с молоком или сливками №378</t>
         </is>
       </c>
       <c r="F27" s="43" t="n">
@@ -1828,7 +1920,7 @@
       <c r="K27" s="44" t="n">
         <v>378</v>
       </c>
-      <c r="L27" s="51" t="n">
+      <c r="L27" s="53" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1861,10 +1953,8 @@
       <c r="J28" s="43" t="n">
         <v>116.82</v>
       </c>
-      <c r="K28" s="44" t="n">
-        <v>878</v>
-      </c>
-      <c r="L28" s="51" t="n">
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="53" t="n">
         <v>8.77</v>
       </c>
     </row>
@@ -1879,7 +1969,7 @@
       </c>
       <c r="E29" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F29" s="43" t="n">
@@ -1900,7 +1990,7 @@
       <c r="K29" s="44" t="n">
         <v>338</v>
       </c>
-      <c r="L29" s="51" t="n">
+      <c r="L29" s="53" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1916,7 +2006,7 @@
       <c r="I30" s="43" t="n"/>
       <c r="J30" s="43" t="n"/>
       <c r="K30" s="44" t="n"/>
-      <c r="L30" s="51" t="n"/>
+      <c r="L30" s="43" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="14" t="n"/>
@@ -1930,7 +2020,7 @@
       <c r="I31" s="43" t="n"/>
       <c r="J31" s="43" t="n"/>
       <c r="K31" s="44" t="n"/>
-      <c r="L31" s="51" t="n"/>
+      <c r="L31" s="43" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="16" t="n"/>
@@ -2005,14 +2095,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="43" t="n"/>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="43" t="n"/>
-      <c r="I34" s="43" t="n"/>
-      <c r="J34" s="43" t="n"/>
-      <c r="K34" s="44" t="n"/>
-      <c r="L34" s="43" t="n"/>
+      <c r="E34" s="42" t="inlineStr">
+        <is>
+          <t>Суп-пюре из картофеля №131</t>
+        </is>
+      </c>
+      <c r="F34" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G34" s="43" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H34" s="43" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="I34" s="43" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J34" s="43" t="n">
+        <v>116.28</v>
+      </c>
+      <c r="K34" s="44" t="n">
+        <v>131</v>
+      </c>
+      <c r="L34" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="14" t="n"/>
@@ -2023,14 +2131,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E35" s="42" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="43" t="n"/>
-      <c r="I35" s="43" t="n"/>
-      <c r="J35" s="43" t="n"/>
+      <c r="E35" s="42" t="inlineStr">
+        <is>
+          <t>Сосиски "Особые халяль"</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G35" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H35" s="43" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I35" s="43" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J35" s="43" t="n">
+        <v>153.43</v>
+      </c>
       <c r="K35" s="44" t="n"/>
-      <c r="L35" s="43" t="n"/>
+      <c r="L35" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="14" t="n"/>
@@ -2041,14 +2165,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E36" s="42" t="n"/>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="43" t="n"/>
-      <c r="H36" s="43" t="n"/>
-      <c r="I36" s="43" t="n"/>
-      <c r="J36" s="43" t="n"/>
-      <c r="K36" s="44" t="n"/>
-      <c r="L36" s="43" t="n"/>
+      <c r="E36" s="42" t="inlineStr">
+        <is>
+          <t>Рис отварной №304</t>
+        </is>
+      </c>
+      <c r="F36" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G36" s="43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H36" s="43" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I36" s="43" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="J36" s="43" t="n">
+        <v>214</v>
+      </c>
+      <c r="K36" s="44" t="n">
+        <v>304</v>
+      </c>
+      <c r="L36" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="14" t="n"/>
@@ -2059,14 +2201,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E37" s="42" t="n"/>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="43" t="n"/>
-      <c r="H37" s="43" t="n"/>
-      <c r="I37" s="43" t="n"/>
-      <c r="J37" s="43" t="n"/>
-      <c r="K37" s="44" t="n"/>
-      <c r="L37" s="43" t="n"/>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G37" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H37" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I37" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J37" s="43" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K37" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L37" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="14" t="n"/>
@@ -2077,14 +2237,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E38" s="42" t="n"/>
-      <c r="F38" s="43" t="n"/>
-      <c r="G38" s="43" t="n"/>
-      <c r="H38" s="43" t="n"/>
-      <c r="I38" s="43" t="n"/>
-      <c r="J38" s="43" t="n"/>
+      <c r="E38" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G38" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H38" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I38" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J38" s="43" t="n">
+        <v>187.04</v>
+      </c>
       <c r="K38" s="44" t="n"/>
-      <c r="L38" s="43" t="n"/>
+      <c r="L38" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="14" t="n"/>
@@ -2177,12 +2353,12 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="C43" s="60" t="inlineStr">
+      <c r="C43" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D43" s="61" t="n"/>
+      <c r="D43" s="63" t="n"/>
       <c r="E43" s="31" t="n"/>
       <c r="F43" s="32">
         <f>F32+F42</f>
@@ -2229,7 +2405,7 @@
       </c>
       <c r="E44" s="39" t="inlineStr">
         <is>
-          <t>Омлет с сыром</t>
+          <t>Омлет с сыром №275</t>
         </is>
       </c>
       <c r="F44" s="40" t="n">
@@ -2245,7 +2421,7 @@
         <v>2.81</v>
       </c>
       <c r="J44" s="40" t="n">
-        <v>287.47</v>
+        <v>276</v>
       </c>
       <c r="K44" s="41" t="n">
         <v>275</v>
@@ -2279,7 +2455,7 @@
       </c>
       <c r="E46" s="42" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="F46" s="43" t="n">
@@ -2295,7 +2471,7 @@
         <v>9.5</v>
       </c>
       <c r="J46" s="43" t="n">
-        <v>36.02</v>
+        <v>39.02</v>
       </c>
       <c r="K46" s="44" t="n">
         <v>459</v>
@@ -2331,11 +2507,9 @@
         <v>24.14</v>
       </c>
       <c r="J47" s="43" t="n">
-        <v>116.88</v>
-      </c>
-      <c r="K47" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>120.88</v>
+      </c>
+      <c r="K47" s="44" t="n"/>
       <c r="L47" s="43" t="n">
         <v>10.58</v>
       </c>
@@ -2351,7 +2525,7 @@
       </c>
       <c r="E48" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F48" s="43" t="n">
@@ -2367,7 +2541,7 @@
         <v>16.8</v>
       </c>
       <c r="J48" s="43" t="n">
-        <v>73.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K48" s="44" t="n">
         <v>338</v>
@@ -2387,7 +2561,7 @@
       </c>
       <c r="E49" s="42" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="F49" s="43" t="n">
@@ -2403,7 +2577,7 @@
         <v>0.13</v>
       </c>
       <c r="J49" s="43" t="n">
-        <v>72.64</v>
+        <v>74.64</v>
       </c>
       <c r="K49" s="44" t="n">
         <v>14</v>
@@ -2481,14 +2655,32 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="E52" s="42" t="n"/>
-      <c r="F52" s="43" t="n"/>
-      <c r="G52" s="43" t="n"/>
-      <c r="H52" s="43" t="n"/>
-      <c r="I52" s="43" t="n"/>
-      <c r="J52" s="43" t="n"/>
-      <c r="K52" s="44" t="n"/>
-      <c r="L52" s="43" t="n"/>
+      <c r="E52" s="42" t="inlineStr">
+        <is>
+          <t>Салат из моркови с сухофруктами №24</t>
+        </is>
+      </c>
+      <c r="F52" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H52" s="43" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I52" s="43" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="J52" s="43" t="n">
+        <v>86</v>
+      </c>
+      <c r="K52" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="L52" s="43" t="n">
+        <v>7.17</v>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="23" t="n"/>
@@ -2499,14 +2691,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E53" s="42" t="n"/>
-      <c r="F53" s="43" t="n"/>
-      <c r="G53" s="43" t="n"/>
-      <c r="H53" s="43" t="n"/>
-      <c r="I53" s="43" t="n"/>
-      <c r="J53" s="43" t="n"/>
-      <c r="K53" s="44" t="n"/>
-      <c r="L53" s="43" t="n"/>
+      <c r="E53" s="42" t="inlineStr">
+        <is>
+          <t>Борщ №81</t>
+        </is>
+      </c>
+      <c r="F53" s="43" t="n">
+        <v>250</v>
+      </c>
+      <c r="G53" s="43" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H53" s="43" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I53" s="43" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="J53" s="43" t="n">
+        <v>171</v>
+      </c>
+      <c r="K53" s="44" t="n">
+        <v>81</v>
+      </c>
+      <c r="L53" s="43" t="n">
+        <v>30.59</v>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="23" t="n"/>
@@ -2517,14 +2727,32 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E54" s="42" t="n"/>
-      <c r="F54" s="43" t="n"/>
-      <c r="G54" s="43" t="n"/>
-      <c r="H54" s="43" t="n"/>
-      <c r="I54" s="43" t="n"/>
-      <c r="J54" s="43" t="n"/>
-      <c r="K54" s="44" t="n"/>
-      <c r="L54" s="43" t="n"/>
+      <c r="E54" s="42" t="inlineStr">
+        <is>
+          <t>Макаронные изделия отварные с маслом №203</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G54" s="43" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="H54" s="43" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I54" s="43" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="J54" s="43" t="n">
+        <v>182</v>
+      </c>
+      <c r="K54" s="44" t="n">
+        <v>203</v>
+      </c>
+      <c r="L54" s="43" t="n">
+        <v>24.52</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="23" t="n"/>
@@ -2553,14 +2781,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E56" s="42" t="n"/>
-      <c r="F56" s="43" t="n"/>
-      <c r="G56" s="43" t="n"/>
-      <c r="H56" s="43" t="n"/>
-      <c r="I56" s="43" t="n"/>
-      <c r="J56" s="43" t="n"/>
-      <c r="K56" s="44" t="n"/>
-      <c r="L56" s="43" t="n"/>
+      <c r="E56" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F56" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G56" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H56" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I56" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J56" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="K56" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L56" s="43" t="n">
+        <v>16.52</v>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="23" t="n"/>
@@ -2571,14 +2817,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E57" s="42" t="n"/>
-      <c r="F57" s="43" t="n"/>
-      <c r="G57" s="43" t="n"/>
-      <c r="H57" s="43" t="n"/>
-      <c r="I57" s="43" t="n"/>
-      <c r="J57" s="43" t="n"/>
+      <c r="E57" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F57" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G57" s="43" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H57" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I57" s="43" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="J57" s="43" t="n">
+        <v>133</v>
+      </c>
       <c r="K57" s="44" t="n"/>
-      <c r="L57" s="43" t="n"/>
+      <c r="L57" s="43" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="23" t="n"/>
@@ -2586,31 +2848,67 @@
       <c r="C58" s="11" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>хлеб черн.</t>
-        </is>
-      </c>
-      <c r="E58" s="42" t="n"/>
-      <c r="F58" s="43" t="n"/>
-      <c r="G58" s="43" t="n"/>
-      <c r="H58" s="43" t="n"/>
-      <c r="I58" s="43" t="n"/>
-      <c r="J58" s="43" t="n"/>
+          <t>кисломол.</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>Масло сливочное (порциями) №14</t>
+        </is>
+      </c>
+      <c r="F58" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" s="43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I58" s="43" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J58" s="43" t="n">
+        <v>75</v>
+      </c>
       <c r="K58" s="44" t="n"/>
-      <c r="L58" s="43" t="n"/>
+      <c r="L58" s="43" t="n">
+        <v>1.11</v>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="23" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="11" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="42" t="n"/>
-      <c r="F59" s="43" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="43" t="n"/>
-      <c r="J59" s="43" t="n"/>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>кисломол.</t>
+        </is>
+      </c>
+      <c r="E59" s="42" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="F59" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H59" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J59" s="43" t="n">
+        <v>19</v>
+      </c>
       <c r="K59" s="44" t="n"/>
-      <c r="L59" s="43" t="n"/>
+      <c r="L59" s="43" t="n">
+        <v>5.69</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="23" t="n"/>
@@ -2671,12 +2969,12 @@
         <f>B44</f>
         <v/>
       </c>
-      <c r="C62" s="60" t="inlineStr">
+      <c r="C62" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D62" s="61" t="n"/>
+      <c r="D62" s="63" t="n"/>
       <c r="E62" s="31" t="n"/>
       <c r="F62" s="32">
         <f>F51+F61</f>
@@ -2723,7 +3021,7 @@
       </c>
       <c r="E63" s="39" t="inlineStr">
         <is>
-          <t>Рис припущенный</t>
+          <t>Рис припущенный №305</t>
         </is>
       </c>
       <c r="F63" s="40" t="n">
@@ -2752,15 +3050,35 @@
       <c r="A64" s="23" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="11" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="42" t="n"/>
-      <c r="F64" s="43" t="n"/>
-      <c r="G64" s="43" t="n"/>
-      <c r="H64" s="43" t="n"/>
-      <c r="I64" s="43" t="n"/>
-      <c r="J64" s="43" t="n"/>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>гор.блюдо</t>
+        </is>
+      </c>
+      <c r="E64" s="42" t="inlineStr">
+        <is>
+          <t>Сосиски "Особые халяль"</t>
+        </is>
+      </c>
+      <c r="F64" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="G64" s="43" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H64" s="43" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I64" s="43" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J64" s="43" t="n">
+        <v>85.23</v>
+      </c>
       <c r="K64" s="44" t="n"/>
-      <c r="L64" s="43" t="n"/>
+      <c r="L64" s="43" t="n">
+        <v>9.18</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="23" t="n"/>
@@ -2773,7 +3091,7 @@
       </c>
       <c r="E65" s="42" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками</t>
+          <t>Чай с молоком или сливками №378</t>
         </is>
       </c>
       <c r="F65" s="43" t="n">
@@ -2827,9 +3145,7 @@
       <c r="J66" s="43" t="n">
         <v>163.58</v>
       </c>
-      <c r="K66" s="44" t="n">
-        <v>878</v>
-      </c>
+      <c r="K66" s="44" t="n"/>
       <c r="L66" s="43" t="n">
         <v>12.85</v>
       </c>
@@ -2845,7 +3161,7 @@
       </c>
       <c r="E67" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F67" s="43" t="n">
@@ -2874,37 +3190,15 @@
       <c r="A68" s="23" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="11" t="n"/>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>гор.блюдо</t>
-        </is>
-      </c>
-      <c r="E68" s="42" t="inlineStr">
-        <is>
-          <t>Сосиски (Особые халяль)</t>
-        </is>
-      </c>
-      <c r="F68" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="G68" s="43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H68" s="43" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="I68" s="43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J68" s="43" t="n">
-        <v>85.23</v>
-      </c>
-      <c r="K68" s="44" t="n">
-        <v>243</v>
-      </c>
-      <c r="L68" s="43" t="n">
-        <v>9.18</v>
-      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="42" t="n"/>
+      <c r="F68" s="43" t="n"/>
+      <c r="G68" s="43" t="n"/>
+      <c r="H68" s="43" t="n"/>
+      <c r="I68" s="43" t="n"/>
+      <c r="J68" s="43" t="n"/>
+      <c r="K68" s="44" t="n"/>
+      <c r="L68" s="43" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="23" t="n"/>
@@ -2993,14 +3287,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E72" s="42" t="n"/>
-      <c r="F72" s="43" t="n"/>
-      <c r="G72" s="43" t="n"/>
-      <c r="H72" s="43" t="n"/>
-      <c r="I72" s="43" t="n"/>
-      <c r="J72" s="43" t="n"/>
-      <c r="K72" s="44" t="n"/>
-      <c r="L72" s="43" t="n"/>
+      <c r="E72" s="42" t="inlineStr">
+        <is>
+          <t>Суп гороховый №127</t>
+        </is>
+      </c>
+      <c r="F72" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G72" s="43" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H72" s="43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I72" s="43" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="J72" s="43" t="n">
+        <v>97.74000000000001</v>
+      </c>
+      <c r="K72" s="44" t="n">
+        <v>127</v>
+      </c>
+      <c r="L72" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="23" t="n"/>
@@ -3011,14 +3323,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E73" s="42" t="n"/>
-      <c r="F73" s="43" t="n"/>
-      <c r="G73" s="43" t="n"/>
-      <c r="H73" s="43" t="n"/>
-      <c r="I73" s="43" t="n"/>
-      <c r="J73" s="43" t="n"/>
+      <c r="E73" s="42" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="F73" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G73" s="43" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H73" s="43" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I73" s="43" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J73" s="43" t="n">
+        <v>281.69</v>
+      </c>
       <c r="K73" s="44" t="n"/>
-      <c r="L73" s="43" t="n"/>
+      <c r="L73" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="23" t="n"/>
@@ -3029,14 +3357,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E74" s="42" t="n"/>
-      <c r="F74" s="43" t="n"/>
-      <c r="G74" s="43" t="n"/>
-      <c r="H74" s="43" t="n"/>
-      <c r="I74" s="43" t="n"/>
-      <c r="J74" s="43" t="n"/>
-      <c r="K74" s="44" t="n"/>
-      <c r="L74" s="43" t="n"/>
+      <c r="E74" s="42" t="inlineStr">
+        <is>
+          <t>Картофельное пюре №377</t>
+        </is>
+      </c>
+      <c r="F74" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G74" s="43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H74" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="43" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J74" s="43" t="n">
+        <v>105</v>
+      </c>
+      <c r="K74" s="44" t="n">
+        <v>377</v>
+      </c>
+      <c r="L74" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="23" t="n"/>
@@ -3047,14 +3393,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E75" s="42" t="n"/>
-      <c r="F75" s="43" t="n"/>
-      <c r="G75" s="43" t="n"/>
-      <c r="H75" s="43" t="n"/>
-      <c r="I75" s="43" t="n"/>
-      <c r="J75" s="43" t="n"/>
-      <c r="K75" s="44" t="n"/>
-      <c r="L75" s="43" t="n"/>
+      <c r="E75" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F75" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G75" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H75" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I75" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J75" s="43" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K75" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L75" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="23" t="n"/>
@@ -3065,14 +3429,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E76" s="42" t="n"/>
-      <c r="F76" s="43" t="n"/>
-      <c r="G76" s="43" t="n"/>
-      <c r="H76" s="43" t="n"/>
-      <c r="I76" s="43" t="n"/>
-      <c r="J76" s="43" t="n"/>
+      <c r="E76" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F76" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G76" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H76" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I76" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J76" s="43" t="n">
+        <v>187.04</v>
+      </c>
       <c r="K76" s="44" t="n"/>
-      <c r="L76" s="43" t="n"/>
+      <c r="L76" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="23" t="n"/>
@@ -3165,12 +3545,12 @@
         <f>B63</f>
         <v/>
       </c>
-      <c r="C81" s="60" t="inlineStr">
+      <c r="C81" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D81" s="61" t="n"/>
+      <c r="D81" s="63" t="n"/>
       <c r="E81" s="31" t="n"/>
       <c r="F81" s="32">
         <f>F70+F80</f>
@@ -3233,10 +3613,10 @@
         <v>0.96</v>
       </c>
       <c r="J82" s="40" t="n">
-        <v>71.64</v>
+        <v>77</v>
       </c>
       <c r="K82" s="41" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="L82" s="40" t="n">
         <v>16.52</v>
@@ -3253,7 +3633,7 @@
       </c>
       <c r="E83" s="42" t="inlineStr">
         <is>
-          <t>Картофельное пюре</t>
+          <t>Картофельное пюре №377</t>
         </is>
       </c>
       <c r="F83" s="43" t="n">
@@ -3263,13 +3643,13 @@
         <v>4.04</v>
       </c>
       <c r="H83" s="43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I83" s="43" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="J83" s="43" t="n">
-        <v>119.96</v>
+        <v>116</v>
       </c>
       <c r="K83" s="44" t="n">
         <v>377</v>
@@ -3289,7 +3669,7 @@
       </c>
       <c r="E84" s="42" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками</t>
+          <t>Чай с молоком или сливками №378</t>
         </is>
       </c>
       <c r="F84" s="43" t="n">
@@ -3305,7 +3685,7 @@
         <v>15.9</v>
       </c>
       <c r="J84" s="43" t="n">
-        <v>81.83</v>
+        <v>82</v>
       </c>
       <c r="K84" s="44" t="n">
         <v>378</v>
@@ -3341,11 +3721,9 @@
         <v>24.14</v>
       </c>
       <c r="J85" s="43" t="n">
-        <v>120.82</v>
-      </c>
-      <c r="K85" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="K85" s="44" t="n"/>
       <c r="L85" s="43" t="n">
         <v>9.18</v>
       </c>
@@ -3379,7 +3757,7 @@
       </c>
       <c r="E87" s="42" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="F87" s="43" t="n">
@@ -3395,7 +3773,7 @@
         <v>0.13</v>
       </c>
       <c r="J87" s="43" t="n">
-        <v>74.64</v>
+        <v>75</v>
       </c>
       <c r="K87" s="44" t="n">
         <v>14</v>
@@ -3473,14 +3851,32 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="E90" s="42" t="n"/>
-      <c r="F90" s="43" t="n"/>
-      <c r="G90" s="43" t="n"/>
-      <c r="H90" s="43" t="n"/>
-      <c r="I90" s="43" t="n"/>
-      <c r="J90" s="43" t="n"/>
-      <c r="K90" s="44" t="n"/>
-      <c r="L90" s="43" t="n"/>
+      <c r="E90" s="42" t="inlineStr">
+        <is>
+          <t>Салат из свеклы с яблоками №28</t>
+        </is>
+      </c>
+      <c r="F90" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="G90" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H90" s="43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I90" s="43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J90" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="K90" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="L90" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="23" t="n"/>
@@ -3491,14 +3887,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E91" s="42" t="n"/>
-      <c r="F91" s="43" t="n"/>
-      <c r="G91" s="43" t="n"/>
-      <c r="H91" s="43" t="n"/>
-      <c r="I91" s="43" t="n"/>
-      <c r="J91" s="43" t="n"/>
-      <c r="K91" s="44" t="n"/>
-      <c r="L91" s="43" t="n"/>
+      <c r="E91" s="42" t="inlineStr">
+        <is>
+          <t>Суп картофельный №112</t>
+        </is>
+      </c>
+      <c r="F91" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G91" s="43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H91" s="43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I91" s="43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J91" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="K91" s="44" t="n">
+        <v>112</v>
+      </c>
+      <c r="L91" s="43" t="n">
+        <v>27.52</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="23" t="n"/>
@@ -3509,14 +3923,32 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E92" s="42" t="n"/>
-      <c r="F92" s="43" t="n"/>
-      <c r="G92" s="43" t="n"/>
-      <c r="H92" s="43" t="n"/>
-      <c r="I92" s="43" t="n"/>
-      <c r="J92" s="43" t="n"/>
-      <c r="K92" s="44" t="n"/>
-      <c r="L92" s="43" t="n"/>
+      <c r="E92" s="42" t="inlineStr">
+        <is>
+          <t>Плов с курицей №291</t>
+        </is>
+      </c>
+      <c r="F92" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G92" s="43" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="H92" s="43" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I92" s="43" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="J92" s="43" t="n">
+        <v>266</v>
+      </c>
+      <c r="K92" s="44" t="n">
+        <v>291</v>
+      </c>
+      <c r="L92" s="43" t="n">
+        <v>30.53</v>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="23" t="n"/>
@@ -3545,14 +3977,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E94" s="42" t="n"/>
-      <c r="F94" s="43" t="n"/>
-      <c r="G94" s="43" t="n"/>
-      <c r="H94" s="43" t="n"/>
-      <c r="I94" s="43" t="n"/>
-      <c r="J94" s="43" t="n"/>
-      <c r="K94" s="44" t="n"/>
-      <c r="L94" s="43" t="n"/>
+      <c r="E94" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F94" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G94" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H94" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I94" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J94" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="K94" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L94" s="43" t="n">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="23" t="n"/>
@@ -3563,14 +4013,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E95" s="42" t="n"/>
-      <c r="F95" s="43" t="n"/>
-      <c r="G95" s="43" t="n"/>
-      <c r="H95" s="43" t="n"/>
-      <c r="I95" s="43" t="n"/>
-      <c r="J95" s="43" t="n"/>
+      <c r="E95" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F95" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="G95" s="43" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="H95" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="43" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="J95" s="43" t="n">
+        <v>241</v>
+      </c>
       <c r="K95" s="44" t="n"/>
-      <c r="L95" s="43" t="n"/>
+      <c r="L95" s="43" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="23" t="n"/>
@@ -3663,12 +4129,12 @@
         <f>B82</f>
         <v/>
       </c>
-      <c r="C100" s="60" t="inlineStr">
+      <c r="C100" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D100" s="61" t="n"/>
+      <c r="D100" s="63" t="n"/>
       <c r="E100" s="31" t="n"/>
       <c r="F100" s="32">
         <f>F89+F99</f>
@@ -3719,7 +4185,7 @@
         </is>
       </c>
       <c r="F101" s="40" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G101" s="40" t="n">
         <v>13</v>
@@ -3731,10 +4197,10 @@
         <v>0.8</v>
       </c>
       <c r="J101" s="40" t="n">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="K101" s="41" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="L101" s="40" t="n">
         <v>13.77</v>
@@ -3751,11 +4217,11 @@
       </c>
       <c r="E102" s="42" t="inlineStr">
         <is>
-          <t>Рис отварной</t>
+          <t>Рис отварной №304</t>
         </is>
       </c>
       <c r="F102" s="43" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G102" s="43" t="n">
         <v>2.43</v>
@@ -3767,7 +4233,7 @@
         <v>24.46</v>
       </c>
       <c r="J102" s="43" t="n">
-        <v>139.78</v>
+        <v>130</v>
       </c>
       <c r="K102" s="44" t="n">
         <v>304</v>
@@ -3785,32 +4251,14 @@
           <t>гор.напиток</t>
         </is>
       </c>
-      <c r="E103" s="42" t="inlineStr">
-        <is>
-          <t>Чай с лимоном</t>
-        </is>
-      </c>
-      <c r="F103" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="G103" s="43" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H103" s="43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I103" s="43" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J103" s="43" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="K103" s="44" t="n">
-        <v>459</v>
-      </c>
-      <c r="L103" s="43" t="n">
-        <v>36.71</v>
-      </c>
+      <c r="E103" s="42" t="n"/>
+      <c r="F103" s="43" t="n"/>
+      <c r="G103" s="43" t="n"/>
+      <c r="H103" s="43" t="n"/>
+      <c r="I103" s="43" t="n"/>
+      <c r="J103" s="43" t="n"/>
+      <c r="K103" s="44" t="n"/>
+      <c r="L103" s="43" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="23" t="n"/>
@@ -3839,13 +4287,11 @@
         <v>24.14</v>
       </c>
       <c r="J104" s="43" t="n">
-        <v>116.82</v>
-      </c>
-      <c r="K104" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="K104" s="44" t="n"/>
       <c r="L104" s="43" t="n">
-        <v>9.18</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -3872,34 +4318,32 @@
       <c r="C106" s="11" t="n"/>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>кисломол.</t>
+          <t>сладкое</t>
         </is>
       </c>
       <c r="E106" s="42" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Булочка домашняя</t>
         </is>
       </c>
       <c r="F106" s="43" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G106" s="43" t="n">
-        <v>0.12</v>
+        <v>4.2</v>
       </c>
       <c r="H106" s="43" t="n">
-        <v>12.3</v>
+        <v>6.7</v>
       </c>
       <c r="I106" s="43" t="n">
-        <v>0.19</v>
+        <v>27.8</v>
       </c>
       <c r="J106" s="43" t="n">
-        <v>111.94</v>
-      </c>
-      <c r="K106" s="44" t="n">
-        <v>14</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="K106" s="44" t="n"/>
       <c r="L106" s="43" t="n">
-        <v>2.75</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
@@ -3908,34 +4352,34 @@
       <c r="C107" s="11" t="n"/>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>булочное</t>
+          <t>кисломол.</t>
         </is>
       </c>
       <c r="E107" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Булочка </t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="F107" s="43" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G107" s="43" t="n">
-        <v>3.8</v>
+        <v>0.12</v>
       </c>
       <c r="H107" s="43" t="n">
-        <v>5.9</v>
+        <v>12.3</v>
       </c>
       <c r="I107" s="43" t="n">
-        <v>9.6</v>
+        <v>0.19</v>
       </c>
       <c r="J107" s="43" t="n">
-        <v>118.75</v>
+        <v>116</v>
       </c>
       <c r="K107" s="44" t="n">
-        <v>428</v>
+        <v>14</v>
       </c>
       <c r="L107" s="43" t="n">
-        <v>11.01</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
@@ -3993,14 +4437,32 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="E109" s="42" t="n"/>
-      <c r="F109" s="43" t="n"/>
-      <c r="G109" s="43" t="n"/>
-      <c r="H109" s="43" t="n"/>
-      <c r="I109" s="43" t="n"/>
-      <c r="J109" s="43" t="n"/>
-      <c r="K109" s="44" t="n"/>
-      <c r="L109" s="43" t="n"/>
+      <c r="E109" s="42" t="inlineStr">
+        <is>
+          <t>Салат из квашеной капусты с луком №9</t>
+        </is>
+      </c>
+      <c r="F109" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G109" s="43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H109" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I109" s="43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J109" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="K109" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="L109" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="23" t="n"/>
@@ -4011,14 +4473,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E110" s="42" t="n"/>
-      <c r="F110" s="43" t="n"/>
-      <c r="G110" s="43" t="n"/>
-      <c r="H110" s="43" t="n"/>
-      <c r="I110" s="43" t="n"/>
-      <c r="J110" s="43" t="n"/>
-      <c r="K110" s="44" t="n"/>
-      <c r="L110" s="43" t="n"/>
+      <c r="E110" s="42" t="inlineStr">
+        <is>
+          <t>Борщ со свежей капустой и томатом №83</t>
+        </is>
+      </c>
+      <c r="F110" s="43" t="n">
+        <v>205</v>
+      </c>
+      <c r="G110" s="43" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H110" s="43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I110" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="J110" s="43" t="n">
+        <v>114</v>
+      </c>
+      <c r="K110" s="44" t="n">
+        <v>83</v>
+      </c>
+      <c r="L110" s="43" t="n">
+        <v>27.52</v>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="23" t="n"/>
@@ -4029,14 +4509,32 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E111" s="42" t="n"/>
-      <c r="F111" s="43" t="n"/>
-      <c r="G111" s="43" t="n"/>
-      <c r="H111" s="43" t="n"/>
-      <c r="I111" s="43" t="n"/>
-      <c r="J111" s="43" t="n"/>
-      <c r="K111" s="44" t="n"/>
-      <c r="L111" s="43" t="n"/>
+      <c r="E111" s="42" t="inlineStr">
+        <is>
+          <t>Макаронные изделия отварные с маслом №203</t>
+        </is>
+      </c>
+      <c r="F111" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G111" s="43" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="H111" s="43" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I111" s="43" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="J111" s="43" t="n">
+        <v>196</v>
+      </c>
+      <c r="K111" s="44" t="n">
+        <v>203</v>
+      </c>
+      <c r="L111" s="43" t="n">
+        <v>30.53</v>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="23" t="n"/>
@@ -4065,14 +4563,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E113" s="42" t="n"/>
-      <c r="F113" s="43" t="n"/>
-      <c r="G113" s="43" t="n"/>
-      <c r="H113" s="43" t="n"/>
-      <c r="I113" s="43" t="n"/>
-      <c r="J113" s="43" t="n"/>
-      <c r="K113" s="44" t="n"/>
-      <c r="L113" s="43" t="n"/>
+      <c r="E113" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F113" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G113" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H113" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I113" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J113" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="K113" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L113" s="43" t="n">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="23" t="n"/>
@@ -4083,14 +4599,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E114" s="42" t="n"/>
-      <c r="F114" s="43" t="n"/>
-      <c r="G114" s="43" t="n"/>
-      <c r="H114" s="43" t="n"/>
-      <c r="I114" s="43" t="n"/>
-      <c r="J114" s="43" t="n"/>
+      <c r="E114" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F114" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G114" s="43" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="H114" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I114" s="43" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="J114" s="43" t="n">
+        <v>185</v>
+      </c>
       <c r="K114" s="44" t="n"/>
-      <c r="L114" s="43" t="n"/>
+      <c r="L114" s="43" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="23" t="n"/>
@@ -4098,17 +4630,35 @@
       <c r="C115" s="11" t="n"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>хлеб черн.</t>
-        </is>
-      </c>
-      <c r="E115" s="42" t="n"/>
-      <c r="F115" s="43" t="n"/>
-      <c r="G115" s="43" t="n"/>
-      <c r="H115" s="43" t="n"/>
-      <c r="I115" s="43" t="n"/>
-      <c r="J115" s="43" t="n"/>
-      <c r="K115" s="44" t="n"/>
-      <c r="L115" s="43" t="n"/>
+          <t>кисломол.</t>
+        </is>
+      </c>
+      <c r="E115" s="42" t="inlineStr">
+        <is>
+          <t>Масло сливочное (порциями) №14</t>
+        </is>
+      </c>
+      <c r="F115" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" s="43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H115" s="43" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I115" s="43" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J115" s="43" t="n">
+        <v>98</v>
+      </c>
+      <c r="K115" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="L115" s="44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="23" t="n"/>
@@ -4183,12 +4733,12 @@
         <f>B101</f>
         <v/>
       </c>
-      <c r="C119" s="60" t="inlineStr">
+      <c r="C119" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D119" s="61" t="n"/>
+      <c r="D119" s="63" t="n"/>
       <c r="E119" s="31" t="n"/>
       <c r="F119" s="32">
         <f>F108+F118</f>
@@ -4235,23 +4785,23 @@
       </c>
       <c r="E120" s="39" t="inlineStr">
         <is>
-          <t>Сырники из творога запеченые</t>
+          <t>Сырники из творога запеченые №286</t>
         </is>
       </c>
       <c r="F120" s="40" t="n">
         <v>150</v>
       </c>
       <c r="G120" s="40" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
       <c r="H120" s="40" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I120" s="40" t="n">
-        <v>19</v>
+        <v>17.9</v>
       </c>
       <c r="J120" s="40" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K120" s="41" t="n">
         <v>286</v>
@@ -4285,7 +4835,7 @@
       </c>
       <c r="E122" s="42" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками</t>
+          <t>Чай с молоком или сливками №378</t>
         </is>
       </c>
       <c r="F122" s="43" t="n">
@@ -4301,7 +4851,7 @@
         <v>15.9</v>
       </c>
       <c r="J122" s="43" t="n">
-        <v>81.83</v>
+        <v>82</v>
       </c>
       <c r="K122" s="44" t="n">
         <v>378</v>
@@ -4337,11 +4887,9 @@
         <v>24.14</v>
       </c>
       <c r="J123" s="43" t="n">
-        <v>116.82</v>
-      </c>
-      <c r="K123" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="K123" s="44" t="n"/>
       <c r="L123" s="43" t="n">
         <v>9.18</v>
       </c>
@@ -4357,7 +4905,7 @@
       </c>
       <c r="E124" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F124" s="43" t="n">
@@ -4373,7 +4921,7 @@
         <v>16.8</v>
       </c>
       <c r="J124" s="43" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="K124" s="44" t="n">
         <v>338</v>
@@ -4386,14 +4934,34 @@
       <c r="A125" s="14" t="n"/>
       <c r="B125" s="15" t="n"/>
       <c r="C125" s="11" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="42" t="n"/>
-      <c r="F125" s="43" t="n"/>
-      <c r="G125" s="43" t="n"/>
-      <c r="H125" s="43" t="n"/>
-      <c r="I125" s="43" t="n"/>
-      <c r="J125" s="43" t="n"/>
-      <c r="K125" s="44" t="n"/>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>кисломол.</t>
+        </is>
+      </c>
+      <c r="E125" s="42" t="inlineStr">
+        <is>
+          <t>Масло сливочное (порциями) №14</t>
+        </is>
+      </c>
+      <c r="F125" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G125" s="43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H125" s="43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I125" s="43" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J125" s="43" t="n">
+        <v>79</v>
+      </c>
+      <c r="K125" s="44" t="n">
+        <v>14</v>
+      </c>
       <c r="L125" s="43" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1">
@@ -4483,14 +5051,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E129" s="42" t="n"/>
-      <c r="F129" s="43" t="n"/>
-      <c r="G129" s="43" t="n"/>
-      <c r="H129" s="43" t="n"/>
-      <c r="I129" s="43" t="n"/>
-      <c r="J129" s="43" t="n"/>
-      <c r="K129" s="44" t="n"/>
-      <c r="L129" s="43" t="n"/>
+      <c r="E129" s="42" t="inlineStr">
+        <is>
+          <t>Суп картофельный с бобовыми №113</t>
+        </is>
+      </c>
+      <c r="F129" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G129" s="43" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H129" s="43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I129" s="43" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="J129" s="43" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="K129" s="44" t="n">
+        <v>113</v>
+      </c>
+      <c r="L129" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="14" t="n"/>
@@ -4501,14 +5087,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E130" s="42" t="n"/>
-      <c r="F130" s="43" t="n"/>
-      <c r="G130" s="43" t="n"/>
-      <c r="H130" s="43" t="n"/>
-      <c r="I130" s="43" t="n"/>
-      <c r="J130" s="43" t="n"/>
+      <c r="E130" s="42" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="F130" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G130" s="43" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H130" s="43" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I130" s="43" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J130" s="43" t="n">
+        <v>262.7</v>
+      </c>
       <c r="K130" s="44" t="n"/>
-      <c r="L130" s="43" t="n"/>
+      <c r="L130" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="14" t="n"/>
@@ -4519,14 +5121,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E131" s="42" t="n"/>
-      <c r="F131" s="43" t="n"/>
-      <c r="G131" s="43" t="n"/>
-      <c r="H131" s="43" t="n"/>
-      <c r="I131" s="43" t="n"/>
-      <c r="J131" s="43" t="n"/>
-      <c r="K131" s="44" t="n"/>
-      <c r="L131" s="43" t="n"/>
+      <c r="E131" s="42" t="inlineStr">
+        <is>
+          <t>Греча отварная №4.3</t>
+        </is>
+      </c>
+      <c r="F131" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G131" s="43" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="H131" s="43" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I131" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J131" s="43" t="n">
+        <v>243.73</v>
+      </c>
+      <c r="K131" s="44" t="n">
+        <v>313</v>
+      </c>
+      <c r="L131" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="14" t="n"/>
@@ -4537,14 +5157,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E132" s="42" t="n"/>
-      <c r="F132" s="43" t="n"/>
-      <c r="G132" s="43" t="n"/>
-      <c r="H132" s="43" t="n"/>
-      <c r="I132" s="43" t="n"/>
-      <c r="J132" s="43" t="n"/>
-      <c r="K132" s="44" t="n"/>
-      <c r="L132" s="43" t="n"/>
+      <c r="E132" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F132" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G132" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H132" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I132" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J132" s="43" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="K132" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L132" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="14" t="n"/>
@@ -4555,14 +5193,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E133" s="42" t="n"/>
-      <c r="F133" s="43" t="n"/>
-      <c r="G133" s="43" t="n"/>
-      <c r="H133" s="43" t="n"/>
-      <c r="I133" s="43" t="n"/>
-      <c r="J133" s="43" t="n"/>
+      <c r="E133" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F133" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G133" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H133" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I133" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J133" s="43" t="n">
+        <v>187.04</v>
+      </c>
       <c r="K133" s="44" t="n"/>
-      <c r="L133" s="43" t="n"/>
+      <c r="L133" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="14" t="n"/>
@@ -4655,12 +5309,12 @@
         <f>B120</f>
         <v/>
       </c>
-      <c r="C138" s="60" t="inlineStr">
+      <c r="C138" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D138" s="61" t="n"/>
+      <c r="D138" s="63" t="n"/>
       <c r="E138" s="31" t="n"/>
       <c r="F138" s="32">
         <f>F127+F137</f>
@@ -4707,7 +5361,7 @@
       </c>
       <c r="E139" s="39" t="inlineStr">
         <is>
-          <t>Запеканка из творога</t>
+          <t>Запеканка из творога №279</t>
         </is>
       </c>
       <c r="F139" s="40" t="n">
@@ -4723,7 +5377,7 @@
         <v>22.5</v>
       </c>
       <c r="J139" s="40" t="n">
-        <v>286.35</v>
+        <v>289.35</v>
       </c>
       <c r="K139" s="41" t="n">
         <v>279</v>
@@ -4757,7 +5411,7 @@
       </c>
       <c r="E141" s="42" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="F141" s="43" t="n">
@@ -4773,7 +5427,7 @@
         <v>9.5</v>
       </c>
       <c r="J141" s="43" t="n">
-        <v>36.02</v>
+        <v>39.02</v>
       </c>
       <c r="K141" s="44" t="n">
         <v>459</v>
@@ -4809,11 +5463,9 @@
         <v>24.14</v>
       </c>
       <c r="J142" s="43" t="n">
-        <v>117.88</v>
-      </c>
-      <c r="K142" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="K142" s="44" t="n"/>
       <c r="L142" s="43" t="n">
         <v>11.01</v>
       </c>
@@ -4829,7 +5481,7 @@
       </c>
       <c r="E143" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F143" s="43" t="n">
@@ -4845,7 +5497,7 @@
         <v>16.8</v>
       </c>
       <c r="J143" s="43" t="n">
-        <v>73.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K143" s="44" t="n">
         <v>338</v>
@@ -4865,7 +5517,7 @@
       </c>
       <c r="E144" s="42" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="F144" s="43" t="n">
@@ -4881,7 +5533,7 @@
         <v>0.13</v>
       </c>
       <c r="J144" s="43" t="n">
-        <v>72.64</v>
+        <v>65</v>
       </c>
       <c r="K144" s="44" t="n">
         <v>14</v>
@@ -4977,14 +5629,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E148" s="42" t="n"/>
-      <c r="F148" s="43" t="n"/>
-      <c r="G148" s="43" t="n"/>
-      <c r="H148" s="43" t="n"/>
-      <c r="I148" s="43" t="n"/>
-      <c r="J148" s="43" t="n"/>
-      <c r="K148" s="44" t="n"/>
-      <c r="L148" s="43" t="n"/>
+      <c r="E148" s="42" t="inlineStr">
+        <is>
+          <t>Суп гороховый №127</t>
+        </is>
+      </c>
+      <c r="F148" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G148" s="43" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H148" s="43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I148" s="43" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="J148" s="43" t="n">
+        <v>98</v>
+      </c>
+      <c r="K148" s="44" t="n">
+        <v>127</v>
+      </c>
+      <c r="L148" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="23" t="n"/>
@@ -4995,14 +5665,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E149" s="42" t="n"/>
-      <c r="F149" s="43" t="n"/>
-      <c r="G149" s="43" t="n"/>
-      <c r="H149" s="43" t="n"/>
-      <c r="I149" s="43" t="n"/>
-      <c r="J149" s="43" t="n"/>
+      <c r="E149" s="42" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="F149" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G149" s="43" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H149" s="43" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I149" s="43" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J149" s="43" t="n">
+        <v>282</v>
+      </c>
       <c r="K149" s="44" t="n"/>
-      <c r="L149" s="43" t="n"/>
+      <c r="L149" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="23" t="n"/>
@@ -5013,14 +5699,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E150" s="42" t="n"/>
-      <c r="F150" s="43" t="n"/>
-      <c r="G150" s="43" t="n"/>
-      <c r="H150" s="43" t="n"/>
-      <c r="I150" s="43" t="n"/>
-      <c r="J150" s="43" t="n"/>
-      <c r="K150" s="44" t="n"/>
-      <c r="L150" s="43" t="n"/>
+      <c r="E150" s="42" t="inlineStr">
+        <is>
+          <t>Рис отварной №304</t>
+        </is>
+      </c>
+      <c r="F150" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G150" s="43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H150" s="43" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I150" s="43" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="J150" s="43" t="n">
+        <v>210</v>
+      </c>
+      <c r="K150" s="44" t="n">
+        <v>304</v>
+      </c>
+      <c r="L150" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="23" t="n"/>
@@ -5031,14 +5735,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E151" s="42" t="n"/>
-      <c r="F151" s="43" t="n"/>
-      <c r="G151" s="43" t="n"/>
-      <c r="H151" s="43" t="n"/>
-      <c r="I151" s="43" t="n"/>
-      <c r="J151" s="43" t="n"/>
-      <c r="K151" s="44" t="n"/>
-      <c r="L151" s="43" t="n"/>
+      <c r="E151" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F151" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G151" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H151" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I151" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J151" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="K151" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L151" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="23" t="n"/>
@@ -5049,14 +5771,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E152" s="42" t="n"/>
-      <c r="F152" s="43" t="n"/>
-      <c r="G152" s="43" t="n"/>
-      <c r="H152" s="43" t="n"/>
-      <c r="I152" s="43" t="n"/>
-      <c r="J152" s="43" t="n"/>
+      <c r="E152" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F152" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G152" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H152" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I152" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J152" s="43" t="n">
+        <v>187</v>
+      </c>
       <c r="K152" s="44" t="n"/>
-      <c r="L152" s="43" t="n"/>
+      <c r="L152" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="23" t="n"/>
@@ -5149,12 +5887,12 @@
         <f>B139</f>
         <v/>
       </c>
-      <c r="C157" s="60" t="inlineStr">
+      <c r="C157" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D157" s="61" t="n"/>
+      <c r="D157" s="63" t="n"/>
       <c r="E157" s="31" t="n"/>
       <c r="F157" s="32">
         <f>F146+F156</f>
@@ -5201,29 +5939,25 @@
       </c>
       <c r="E158" s="39" t="inlineStr">
         <is>
-          <t>Греча отварная</t>
+          <t>Котлета куриная</t>
         </is>
       </c>
       <c r="F158" s="40" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G158" s="40" t="n">
-        <v>5.73</v>
+        <v>6.65</v>
       </c>
       <c r="H158" s="40" t="n">
-        <v>4.06</v>
+        <v>12.6</v>
       </c>
       <c r="I158" s="40" t="n">
-        <v>25.76</v>
+        <v>19.6</v>
       </c>
       <c r="J158" s="40" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="K158" s="41" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="K158" s="41" t="n"/>
       <c r="L158" s="40" t="n">
         <v>18.35</v>
       </c>
@@ -5239,26 +5973,26 @@
       </c>
       <c r="E159" s="42" t="inlineStr">
         <is>
-          <t>Котлета куриная</t>
+          <t>Греча отварная №4,3</t>
         </is>
       </c>
       <c r="F159" s="43" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G159" s="43" t="n">
-        <v>6.65</v>
+        <v>5.73</v>
       </c>
       <c r="H159" s="43" t="n">
-        <v>12.6</v>
+        <v>4.06</v>
       </c>
       <c r="I159" s="43" t="n">
-        <v>19.6</v>
+        <v>25.76</v>
       </c>
       <c r="J159" s="43" t="n">
-        <v>210.4</v>
+        <v>151</v>
       </c>
       <c r="K159" s="44" t="n">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="L159" s="43" t="n">
         <v>12.85</v>
@@ -5275,7 +6009,7 @@
       </c>
       <c r="E160" s="42" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="F160" s="43" t="n">
@@ -5291,7 +6025,7 @@
         <v>9.5</v>
       </c>
       <c r="J160" s="43" t="n">
-        <v>36.02</v>
+        <v>39</v>
       </c>
       <c r="K160" s="44" t="n">
         <v>459</v>
@@ -5327,11 +6061,9 @@
         <v>24.14</v>
       </c>
       <c r="J161" s="43" t="n">
-        <v>116.82</v>
-      </c>
-      <c r="K161" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="K161" s="44" t="n"/>
       <c r="L161" s="43" t="n">
         <v>9.18</v>
       </c>
@@ -5347,7 +6079,7 @@
       </c>
       <c r="E162" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F162" s="43" t="n">
@@ -5363,7 +6095,7 @@
         <v>16.8</v>
       </c>
       <c r="J162" s="43" t="n">
-        <v>73.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="K162" s="44" t="n">
         <v>338</v>
@@ -5455,14 +6187,32 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="E166" s="42" t="n"/>
-      <c r="F166" s="43" t="n"/>
-      <c r="G166" s="43" t="n"/>
-      <c r="H166" s="43" t="n"/>
-      <c r="I166" s="43" t="n"/>
-      <c r="J166" s="43" t="n"/>
-      <c r="K166" s="44" t="n"/>
-      <c r="L166" s="43" t="n"/>
+      <c r="E166" s="42" t="inlineStr">
+        <is>
+          <t>Салат из моркови с сухофруктами №24</t>
+        </is>
+      </c>
+      <c r="F166" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G166" s="43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H166" s="43" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="I166" s="43" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="J166" s="43" t="n">
+        <v>87</v>
+      </c>
+      <c r="K166" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="L166" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="A167" s="23" t="n"/>
@@ -5473,14 +6223,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E167" s="42" t="n"/>
-      <c r="F167" s="43" t="n"/>
-      <c r="G167" s="43" t="n"/>
-      <c r="H167" s="43" t="n"/>
-      <c r="I167" s="43" t="n"/>
-      <c r="J167" s="43" t="n"/>
-      <c r="K167" s="44" t="n"/>
-      <c r="L167" s="43" t="n"/>
+      <c r="E167" s="42" t="inlineStr">
+        <is>
+          <t>Суп с фасолью №119</t>
+        </is>
+      </c>
+      <c r="F167" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G167" s="43" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="H167" s="43" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I167" s="43" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="J167" s="43" t="n">
+        <v>241</v>
+      </c>
+      <c r="K167" s="44" t="n">
+        <v>119</v>
+      </c>
+      <c r="L167" s="43" t="n">
+        <v>27.52</v>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="23" t="n"/>
@@ -5491,14 +6259,32 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E168" s="42" t="n"/>
-      <c r="F168" s="43" t="n"/>
-      <c r="G168" s="43" t="n"/>
-      <c r="H168" s="43" t="n"/>
-      <c r="I168" s="43" t="n"/>
-      <c r="J168" s="43" t="n"/>
-      <c r="K168" s="44" t="n"/>
-      <c r="L168" s="43" t="n"/>
+      <c r="E168" s="42" t="inlineStr">
+        <is>
+          <t>Плов с курицей №291</t>
+        </is>
+      </c>
+      <c r="F168" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G168" s="43" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="H168" s="43" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I168" s="43" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="J168" s="43" t="n">
+        <v>220</v>
+      </c>
+      <c r="K168" s="44" t="n">
+        <v>291</v>
+      </c>
+      <c r="L168" s="43" t="n">
+        <v>30.53</v>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="A169" s="23" t="n"/>
@@ -5527,14 +6313,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E170" s="42" t="n"/>
-      <c r="F170" s="43" t="n"/>
-      <c r="G170" s="43" t="n"/>
-      <c r="H170" s="43" t="n"/>
-      <c r="I170" s="43" t="n"/>
-      <c r="J170" s="43" t="n"/>
-      <c r="K170" s="44" t="n"/>
-      <c r="L170" s="43" t="n"/>
+      <c r="E170" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F170" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G170" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H170" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I170" s="43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J170" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="K170" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L170" s="43" t="n">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="23" t="n"/>
@@ -5545,14 +6349,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E171" s="42" t="n"/>
-      <c r="F171" s="43" t="n"/>
-      <c r="G171" s="43" t="n"/>
-      <c r="H171" s="43" t="n"/>
-      <c r="I171" s="43" t="n"/>
-      <c r="J171" s="43" t="n"/>
+      <c r="E171" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F171" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G171" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H171" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I171" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J171" s="43" t="n">
+        <v>171</v>
+      </c>
       <c r="K171" s="44" t="n"/>
-      <c r="L171" s="43" t="n"/>
+      <c r="L171" s="43" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="23" t="n"/>
@@ -5645,12 +6465,12 @@
         <f>B158</f>
         <v/>
       </c>
-      <c r="C176" s="60" t="inlineStr">
+      <c r="C176" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D176" s="61" t="n"/>
+      <c r="D176" s="63" t="n"/>
       <c r="E176" s="31" t="n"/>
       <c r="F176" s="32">
         <f>F165+F175</f>
@@ -5697,27 +6517,25 @@
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Рис отварной</t>
+          <t>Котлета куриная</t>
         </is>
       </c>
       <c r="F177" s="40" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G177" s="40" t="n">
-        <v>2.43</v>
+        <v>6.65</v>
       </c>
       <c r="H177" s="40" t="n">
-        <v>3.58</v>
+        <v>12.6</v>
       </c>
       <c r="I177" s="40" t="n">
-        <v>24.46</v>
+        <v>19.6</v>
       </c>
       <c r="J177" s="40" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="K177" s="41" t="n">
-        <v>304</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="K177" s="41" t="n"/>
       <c r="L177" s="40" t="n">
         <v>18.35</v>
       </c>
@@ -5733,26 +6551,26 @@
       </c>
       <c r="E178" s="42" t="inlineStr">
         <is>
-          <t>Котлета куриная</t>
+          <t>Рис отварной №304</t>
         </is>
       </c>
       <c r="F178" s="43" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G178" s="43" t="n">
-        <v>6.65</v>
+        <v>2.43</v>
       </c>
       <c r="H178" s="43" t="n">
-        <v>12.6</v>
+        <v>3.58</v>
       </c>
       <c r="I178" s="43" t="n">
-        <v>19.6</v>
+        <v>24.46</v>
       </c>
       <c r="J178" s="43" t="n">
-        <v>210.4</v>
+        <v>130</v>
       </c>
       <c r="K178" s="44" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="L178" s="43" t="n">
         <v>12.85</v>
@@ -5769,7 +6587,7 @@
       </c>
       <c r="E179" s="42" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="F179" s="43" t="n">
@@ -5785,7 +6603,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="J179" s="43" t="n">
-        <v>35.09</v>
+        <v>35</v>
       </c>
       <c r="K179" s="44" t="n">
         <v>459</v>
@@ -5821,11 +6639,9 @@
         <v>24.14</v>
       </c>
       <c r="J180" s="43" t="n">
-        <v>116.88</v>
-      </c>
-      <c r="K180" s="44" t="n">
-        <v>878</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="K180" s="44" t="n"/>
       <c r="L180" s="43" t="n">
         <v>9.18</v>
       </c>
@@ -5841,7 +6657,7 @@
       </c>
       <c r="E181" s="42" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="F181" s="43" t="n">
@@ -5857,7 +6673,7 @@
         <v>16.8</v>
       </c>
       <c r="J181" s="43" t="n">
-        <v>73.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="K181" s="44" t="n">
         <v>338</v>
@@ -5967,14 +6783,32 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="E186" s="42" t="n"/>
-      <c r="F186" s="43" t="n"/>
-      <c r="G186" s="43" t="n"/>
-      <c r="H186" s="43" t="n"/>
-      <c r="I186" s="43" t="n"/>
-      <c r="J186" s="43" t="n"/>
-      <c r="K186" s="44" t="n"/>
-      <c r="L186" s="43" t="n"/>
+      <c r="E186" s="42" t="inlineStr">
+        <is>
+          <t>Суп гороховый №127</t>
+        </is>
+      </c>
+      <c r="F186" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G186" s="43" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H186" s="43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I186" s="43" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="J186" s="43" t="n">
+        <v>98</v>
+      </c>
+      <c r="K186" s="44" t="n">
+        <v>127</v>
+      </c>
+      <c r="L186" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="23" t="n"/>
@@ -5985,14 +6819,30 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="E187" s="42" t="n"/>
-      <c r="F187" s="43" t="n"/>
-      <c r="G187" s="43" t="n"/>
-      <c r="H187" s="43" t="n"/>
-      <c r="I187" s="43" t="n"/>
-      <c r="J187" s="43" t="n"/>
+      <c r="E187" s="42" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="F187" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G187" s="43" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H187" s="43" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I187" s="43" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J187" s="43" t="n">
+        <v>282</v>
+      </c>
       <c r="K187" s="44" t="n"/>
-      <c r="L187" s="43" t="n"/>
+      <c r="L187" s="43" t="n">
+        <v>23.25</v>
+      </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="23" t="n"/>
@@ -6003,14 +6853,32 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="E188" s="42" t="n"/>
-      <c r="F188" s="43" t="n"/>
-      <c r="G188" s="43" t="n"/>
-      <c r="H188" s="43" t="n"/>
-      <c r="I188" s="43" t="n"/>
-      <c r="J188" s="43" t="n"/>
-      <c r="K188" s="44" t="n"/>
-      <c r="L188" s="43" t="n"/>
+      <c r="E188" s="42" t="inlineStr">
+        <is>
+          <t>Рис отварной №304</t>
+        </is>
+      </c>
+      <c r="F188" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="G188" s="43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H188" s="43" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I188" s="43" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="J188" s="43" t="n">
+        <v>210</v>
+      </c>
+      <c r="K188" s="44" t="n">
+        <v>304</v>
+      </c>
+      <c r="L188" s="43" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1">
       <c r="A189" s="23" t="n"/>
@@ -6021,14 +6889,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="E189" s="42" t="n"/>
-      <c r="F189" s="43" t="n"/>
-      <c r="G189" s="43" t="n"/>
-      <c r="H189" s="43" t="n"/>
-      <c r="I189" s="43" t="n"/>
-      <c r="J189" s="43" t="n"/>
-      <c r="K189" s="44" t="n"/>
-      <c r="L189" s="43" t="n"/>
+      <c r="E189" s="42" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="F189" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="G189" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H189" s="43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I189" s="43" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J189" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="K189" s="44" t="n">
+        <v>459</v>
+      </c>
+      <c r="L189" s="43" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="23" t="n"/>
@@ -6039,14 +6925,30 @@
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="E190" s="42" t="n"/>
-      <c r="F190" s="43" t="n"/>
-      <c r="G190" s="43" t="n"/>
-      <c r="H190" s="43" t="n"/>
-      <c r="I190" s="43" t="n"/>
-      <c r="J190" s="43" t="n"/>
+      <c r="E190" s="42" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="F190" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G190" s="43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="H190" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I190" s="43" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J190" s="43" t="n">
+        <v>187</v>
+      </c>
       <c r="K190" s="44" t="n"/>
-      <c r="L190" s="43" t="n"/>
+      <c r="L190" s="43" t="n">
+        <v>27.73</v>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1">
       <c r="A191" s="23" t="n"/>
@@ -6139,12 +7041,12 @@
         <f>B177</f>
         <v/>
       </c>
-      <c r="C195" s="60" t="inlineStr">
+      <c r="C195" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D195" s="61" t="n"/>
+      <c r="D195" s="63" t="n"/>
       <c r="E195" s="31" t="n"/>
       <c r="F195" s="32">
         <f>F184+F194</f>
@@ -6175,13 +7077,13 @@
     <row r="196" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="27" t="n"/>
       <c r="B196" s="28" t="n"/>
-      <c r="C196" s="54" t="inlineStr">
+      <c r="C196" s="56" t="inlineStr">
         <is>
           <t>Среднее значение за период:</t>
         </is>
       </c>
-      <c r="D196" s="62" t="n"/>
-      <c r="E196" s="63" t="n"/>
+      <c r="D196" s="64" t="n"/>
+      <c r="E196" s="65" t="n"/>
       <c r="F196" s="34">
         <f>(F24+F43+F62+F81+F100+F119+F138+F157+F176+F195)/(IF(F24=0,0,1)+IF(F43=0,0,1)+IF(F62=0,0,1)+IF(F81=0,0,1)+IF(F100=0,0,1)+IF(F119=0,0,1)+IF(F138=0,0,1)+IF(F157=0,0,1)+IF(F176=0,0,1)+IF(F195=0,0,1))</f>
         <v/>
@@ -6226,6 +7128,6 @@
     <mergeCell ref="C196:E196"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="61"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/83/food/tm2026-sm.xlsx
+++ b/83/food/tm2026-sm.xlsx
@@ -7115,8 +7115,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>
